--- a/v1/Library/Recipes/excel/02-Dielsalder_hydrogel_96_combinations_05.xlsx
+++ b/v1/Library/Recipes/excel/02-Dielsalder_hydrogel_96_combinations_05.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unimibit-my.sharepoint.com/personal/marco_piazzoni_unimib_it/Documents/MRC-Lab/Progetti/11 - Automazione/opentrons/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\LabOS\v1\Library\Recipes\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_F25DC773A252ABDACC10487A81596E505ADE58ED" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F45D2571-36E7-400B-A8F6-101F74AA89A8}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2ABFAD7A-4BA8-4AE9-8DF8-A1A4200D94CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -381,7 +381,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normale" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -660,16 +660,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E97"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.88671875" style="1"/>
-    <col min="2" max="2" width="19.6640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18.88671875" style="2" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.85546875" style="1"/>
+    <col min="2" max="2" width="19.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.85546875" style="2" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="33" style="2" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="18" style="2" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -686,7 +686,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>5</v>
       </c>
@@ -703,7 +703,7 @@
         <v>2.5000000000000001E-2</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
@@ -720,7 +720,7 @@
         <v>3.5000000000000003E-2</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>7</v>
       </c>
@@ -737,7 +737,7 @@
         <v>4.4999999999999998E-2</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>8</v>
       </c>
@@ -754,7 +754,7 @@
         <v>5.5E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>9</v>
       </c>
@@ -771,7 +771,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>10</v>
       </c>
@@ -788,7 +788,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>11</v>
       </c>
@@ -805,7 +805,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>12</v>
       </c>
@@ -822,7 +822,7 @@
         <v>7.4999999999999997E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>13</v>
       </c>
@@ -839,7 +839,7 @@
         <v>3.5000000000000003E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>14</v>
       </c>
@@ -856,7 +856,7 @@
         <v>4.4999999999999998E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>15</v>
       </c>
@@ -873,7 +873,7 @@
         <v>5.5E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>16</v>
       </c>
@@ -890,7 +890,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>17</v>
       </c>
@@ -907,7 +907,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>18</v>
       </c>
@@ -924,7 +924,7 @@
         <v>7.4999999999999997E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>19</v>
       </c>
@@ -941,7 +941,7 @@
         <v>0.08</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>20</v>
       </c>
@@ -958,7 +958,7 @@
         <v>8.5000000000000006E-2</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>21</v>
       </c>
@@ -975,7 +975,7 @@
         <v>4.2999999999999997E-2</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>22</v>
       </c>
@@ -992,7 +992,7 @@
         <v>5.2999999999999999E-2</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>23</v>
       </c>
@@ -1009,7 +1009,7 @@
         <v>6.3E-2</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>24</v>
       </c>
@@ -1026,7 +1026,7 @@
         <v>7.2999999999999995E-2</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>25</v>
       </c>
@@ -1043,7 +1043,7 @@
         <v>7.8E-2</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>26</v>
       </c>
@@ -1060,7 +1060,7 @@
         <v>8.3000000000000004E-2</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>27</v>
       </c>
@@ -1077,7 +1077,7 @@
         <v>8.7999999999999995E-2</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>28</v>
       </c>
@@ -1094,7 +1094,7 @@
         <v>9.2999999999999999E-2</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>29</v>
       </c>
@@ -1111,7 +1111,7 @@
         <v>4.4999999999999998E-2</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>30</v>
       </c>
@@ -1128,7 +1128,7 @@
         <v>5.5E-2</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
         <v>31</v>
       </c>
@@ -1145,7 +1145,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
         <v>32</v>
       </c>
@@ -1162,7 +1162,7 @@
         <v>7.4999999999999997E-2</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
         <v>33</v>
       </c>
@@ -1179,7 +1179,7 @@
         <v>0.08</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
         <v>34</v>
       </c>
@@ -1196,7 +1196,7 @@
         <v>8.5000000000000006E-2</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
         <v>35</v>
       </c>
@@ -1213,7 +1213,7 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
         <v>36</v>
       </c>
@@ -1230,7 +1230,7 @@
         <v>9.5000000000000001E-2</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
         <v>37</v>
       </c>
@@ -1247,7 +1247,7 @@
         <v>2.9000000000000001E-2</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
         <v>38</v>
       </c>
@@ -1264,7 +1264,7 @@
         <v>3.9E-2</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
         <v>39</v>
       </c>
@@ -1281,7 +1281,7 @@
         <v>4.9000000000000002E-2</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
         <v>40</v>
       </c>
@@ -1298,7 +1298,7 @@
         <v>5.8999999999999997E-2</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
         <v>41</v>
       </c>
@@ -1315,7 +1315,7 @@
         <v>6.4000000000000001E-2</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
         <v>42</v>
       </c>
@@ -1332,7 +1332,7 @@
         <v>6.9000000000000006E-2</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
         <v>43</v>
       </c>
@@ -1349,7 +1349,7 @@
         <v>7.3999999999999996E-2</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
         <v>44</v>
       </c>
@@ -1366,7 +1366,7 @@
         <v>7.9000000000000001E-2</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
         <v>45</v>
       </c>
@@ -1383,7 +1383,7 @@
         <v>3.9E-2</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
         <v>46</v>
       </c>
@@ -1400,7 +1400,7 @@
         <v>4.9000000000000002E-2</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
         <v>47</v>
       </c>
@@ -1417,7 +1417,7 @@
         <v>5.8999999999999997E-2</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
         <v>48</v>
       </c>
@@ -1434,7 +1434,7 @@
         <v>6.9000000000000006E-2</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
         <v>49</v>
       </c>
@@ -1451,7 +1451,7 @@
         <v>7.3999999999999996E-2</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
         <v>50</v>
       </c>
@@ -1468,7 +1468,7 @@
         <v>7.9000000000000001E-2</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
         <v>51</v>
       </c>
@@ -1485,7 +1485,7 @@
         <v>8.4000000000000005E-2</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
         <v>52</v>
       </c>
@@ -1502,7 +1502,7 @@
         <v>8.8999999999999996E-2</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
         <v>53</v>
       </c>
@@ -1519,7 +1519,7 @@
         <v>4.7E-2</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
         <v>54</v>
       </c>
@@ -1536,7 +1536,7 @@
         <v>5.7000000000000002E-2</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
         <v>55</v>
       </c>
@@ -1553,7 +1553,7 @@
         <v>6.7000000000000004E-2</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
         <v>56</v>
       </c>
@@ -1570,7 +1570,7 @@
         <v>7.6999999999999999E-2</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
         <v>57</v>
       </c>
@@ -1587,7 +1587,7 @@
         <v>8.2000000000000003E-2</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
         <v>58</v>
       </c>
@@ -1604,7 +1604,7 @@
         <v>8.6999999999999994E-2</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
         <v>59</v>
       </c>
@@ -1621,7 +1621,7 @@
         <v>9.1999999999999998E-2</v>
       </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
         <v>60</v>
       </c>
@@ -1638,7 +1638,7 @@
         <v>9.7000000000000003E-2</v>
       </c>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
         <v>61</v>
       </c>
@@ -1655,7 +1655,7 @@
         <v>4.9000000000000002E-2</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
         <v>62</v>
       </c>
@@ -1672,7 +1672,7 @@
         <v>5.8999999999999997E-2</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
         <v>63</v>
       </c>
@@ -1689,7 +1689,7 @@
         <v>6.9000000000000006E-2</v>
       </c>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
         <v>64</v>
       </c>
@@ -1706,7 +1706,7 @@
         <v>7.9000000000000001E-2</v>
       </c>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
         <v>65</v>
       </c>
@@ -1723,7 +1723,7 @@
         <v>8.4000000000000005E-2</v>
       </c>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
         <v>66</v>
       </c>
@@ -1740,7 +1740,7 @@
         <v>8.8999999999999996E-2</v>
       </c>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
         <v>67</v>
       </c>
@@ -1757,7 +1757,7 @@
         <v>9.4E-2</v>
       </c>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
         <v>68</v>
       </c>
@@ -1774,7 +1774,7 @@
         <v>9.9000000000000005E-2</v>
       </c>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
         <v>69</v>
       </c>
@@ -1791,7 +1791,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
         <v>70</v>
       </c>
@@ -1808,7 +1808,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
         <v>71</v>
       </c>
@@ -1825,7 +1825,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
         <v>72</v>
       </c>
@@ -1842,7 +1842,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
         <v>73</v>
       </c>
@@ -1859,7 +1859,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
         <v>74</v>
       </c>
@@ -1876,7 +1876,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
         <v>75</v>
       </c>
@@ -1893,7 +1893,7 @@
         <v>7.4999999999999997E-2</v>
       </c>
     </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
         <v>76</v>
       </c>
@@ -1910,7 +1910,7 @@
         <v>0.08</v>
       </c>
     </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
         <v>77</v>
       </c>
@@ -1927,7 +1927,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
         <v>78</v>
       </c>
@@ -1944,7 +1944,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
         <v>79</v>
       </c>
@@ -1961,7 +1961,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
         <v>80</v>
       </c>
@@ -1978,7 +1978,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
         <v>81</v>
       </c>
@@ -1995,7 +1995,7 @@
         <v>7.4999999999999997E-2</v>
       </c>
     </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
         <v>82</v>
       </c>
@@ -2012,7 +2012,7 @@
         <v>0.08</v>
       </c>
     </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
         <v>83</v>
       </c>
@@ -2029,7 +2029,7 @@
         <v>8.5000000000000006E-2</v>
       </c>
     </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
         <v>84</v>
       </c>
@@ -2046,7 +2046,7 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
         <v>85</v>
       </c>
@@ -2063,7 +2063,7 @@
         <v>4.8000000000000001E-2</v>
       </c>
     </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
         <v>86</v>
       </c>
@@ -2080,7 +2080,7 @@
         <v>5.8000000000000003E-2</v>
       </c>
     </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
         <v>87</v>
       </c>
@@ -2097,7 +2097,7 @@
         <v>6.8000000000000005E-2</v>
       </c>
     </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
         <v>88</v>
       </c>
@@ -2114,7 +2114,7 @@
         <v>7.8E-2</v>
       </c>
     </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
         <v>89</v>
       </c>
@@ -2131,7 +2131,7 @@
         <v>8.3000000000000004E-2</v>
       </c>
     </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
         <v>90</v>
       </c>
@@ -2148,7 +2148,7 @@
         <v>8.7999999999999995E-2</v>
       </c>
     </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
         <v>91</v>
       </c>
@@ -2165,7 +2165,7 @@
         <v>9.2999999999999999E-2</v>
       </c>
     </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
         <v>92</v>
       </c>
@@ -2182,7 +2182,7 @@
         <v>9.8000000000000004E-2</v>
       </c>
     </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
         <v>93</v>
       </c>
@@ -2199,7 +2199,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
         <v>94</v>
       </c>
@@ -2216,7 +2216,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
         <v>95</v>
       </c>
@@ -2233,7 +2233,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
         <v>96</v>
       </c>
@@ -2250,7 +2250,7 @@
         <v>0.08</v>
       </c>
     </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
         <v>97</v>
       </c>
@@ -2267,7 +2267,7 @@
         <v>8.5000000000000006E-2</v>
       </c>
     </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
         <v>98</v>
       </c>
@@ -2284,7 +2284,7 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
         <v>99</v>
       </c>
@@ -2301,7 +2301,7 @@
         <v>9.5000000000000001E-2</v>
       </c>
     </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
         <v>100</v>
       </c>
